--- a/grupos/4AEM - Estadisticos 20232.xlsx
+++ b/grupos/4AEM - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="94">
   <si>
     <t>Materia</t>
   </si>
@@ -191,15 +191,15 @@
     <t>Rivera Cruz Ezequiel</t>
   </si>
   <si>
+    <t>Faltante Faltante Faltante</t>
+  </si>
+  <si>
+    <t>Jiménez Nieto Enrique</t>
+  </si>
+  <si>
     <t>Hernández Castro Enrique</t>
   </si>
   <si>
-    <t>Faltante Faltante Faltante</t>
-  </si>
-  <si>
-    <t>Jiménez Nieto Enrique</t>
-  </si>
-  <si>
     <t>Cruz Alejo José Armando</t>
   </si>
   <si>
@@ -215,109 +215,91 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>APALE</t>
+  </si>
+  <si>
     <t>CRUZ</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
     <t>GUERRA</t>
   </si>
   <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>MERINO</t>
+  </si>
+  <si>
+    <t>PANZO</t>
+  </si>
+  <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>BASILIO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MERINO</t>
-  </si>
-  <si>
-    <t>PANZO</t>
+    <t>TEXOCO</t>
   </si>
   <si>
     <t>COYOHUA</t>
   </si>
   <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
     <t>JERONIMO</t>
   </si>
   <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>QUERO</t>
+  </si>
+  <si>
+    <t>AVELINO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>MACARIO</t>
+  </si>
+  <si>
     <t>RAMOS</t>
   </si>
   <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
-    <t>ANGEL</t>
-  </si>
-  <si>
-    <t>AVELINO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>ZARATE</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
+    <t>DANIEL</t>
   </si>
   <si>
     <t>DIEGO</t>
   </si>
   <si>
-    <t>CRISTHIAN</t>
-  </si>
-  <si>
     <t>LUIS</t>
   </si>
   <si>
+    <t>RUBEN DE JESUS</t>
+  </si>
+  <si>
+    <t>DIEGO JESUS</t>
+  </si>
+  <si>
+    <t>KEVIN</t>
+  </si>
+  <si>
+    <t>ALEXANDER</t>
+  </si>
+  <si>
+    <t>CESAR</t>
+  </si>
+  <si>
+    <t>SHERLIN</t>
+  </si>
+  <si>
     <t>ANGEL GUILLERMO</t>
-  </si>
-  <si>
-    <t>RUBEN DE JESUS</t>
-  </si>
-  <si>
-    <t>RICARDO</t>
-  </si>
-  <si>
-    <t>ISABEL</t>
-  </si>
-  <si>
-    <t>KEVIN</t>
-  </si>
-  <si>
-    <t>ALEXANDER</t>
-  </si>
-  <si>
-    <t>OSMAR UZIEL</t>
-  </si>
-  <si>
-    <t>CESAR</t>
-  </si>
-  <si>
-    <t>SHERLIN</t>
   </si>
 </sst>
 </file>
@@ -844,25 +826,25 @@
         <v>10</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -892,7 +874,7 @@
         <v>9</v>
       </c>
       <c r="Y4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z4">
         <v>10</v>
@@ -933,25 +915,25 @@
         <v>10</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -978,22 +960,22 @@
         <v>5</v>
       </c>
       <c r="X5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA5">
         <v>8</v>
       </c>
       <c r="AB5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC5">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -1022,25 +1004,25 @@
         <v>8</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1067,10 +1049,10 @@
         <v>5</v>
       </c>
       <c r="X6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y6">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z6">
         <v>5</v>
@@ -1079,10 +1061,10 @@
         <v>8</v>
       </c>
       <c r="AB6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC6">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1111,25 +1093,25 @@
         <v>10</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1159,7 +1141,7 @@
         <v>10</v>
       </c>
       <c r="Y7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z7">
         <v>10</v>
@@ -1168,7 +1150,7 @@
         <v>8</v>
       </c>
       <c r="AB7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC7">
         <v>10</v>
@@ -1200,25 +1182,25 @@
         <v>9</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1242,25 +1224,25 @@
         <v>-1</v>
       </c>
       <c r="W8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X8">
         <v>8</v>
       </c>
       <c r="Y8">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA8">
         <v>8</v>
       </c>
       <c r="AB8">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC8">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1289,25 +1271,25 @@
         <v>5</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1340,7 +1322,7 @@
         <v>6</v>
       </c>
       <c r="Z9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA9">
         <v>8</v>
@@ -1378,25 +1360,25 @@
         <v>10</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1426,16 +1408,16 @@
         <v>9</v>
       </c>
       <c r="Y10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA10">
         <v>8</v>
       </c>
       <c r="AB10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC10">
         <v>10</v>
@@ -1467,25 +1449,25 @@
         <v>7</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1524,10 +1506,10 @@
         <v>8</v>
       </c>
       <c r="AB11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC11">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1556,25 +1538,25 @@
         <v>10</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1604,16 +1586,16 @@
         <v>8</v>
       </c>
       <c r="Y12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA12">
         <v>8</v>
       </c>
       <c r="AB12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC12">
         <v>10</v>
@@ -1645,25 +1627,25 @@
         <v>6</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1690,10 +1672,10 @@
         <v>5</v>
       </c>
       <c r="X13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z13">
         <v>5</v>
@@ -1702,7 +1684,7 @@
         <v>8</v>
       </c>
       <c r="AB13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC13">
         <v>6</v>
@@ -1734,25 +1716,25 @@
         <v>9</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1776,22 +1758,22 @@
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA14">
         <v>8</v>
       </c>
       <c r="AB14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC14">
         <v>9</v>
@@ -1823,25 +1805,25 @@
         <v>7</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1868,13 +1850,13 @@
         <v>5</v>
       </c>
       <c r="X15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA15">
         <v>8</v>
@@ -1883,7 +1865,7 @@
         <v>7</v>
       </c>
       <c r="AC15">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -1912,25 +1894,25 @@
         <v>9</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -1957,7 +1939,7 @@
         <v>6</v>
       </c>
       <c r="X16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y16">
         <v>8</v>
@@ -1969,10 +1951,10 @@
         <v>8</v>
       </c>
       <c r="AB16">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC16">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -2001,25 +1983,25 @@
         <v>10</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -2043,13 +2025,13 @@
         <v>-1</v>
       </c>
       <c r="W17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z17">
         <v>10</v>
@@ -2058,7 +2040,7 @@
         <v>8</v>
       </c>
       <c r="AB17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC17">
         <v>10</v>
@@ -2090,25 +2072,25 @@
         <v>8</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2138,19 +2120,19 @@
         <v>5</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA18">
         <v>8</v>
       </c>
       <c r="AB18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC18">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2179,25 +2161,25 @@
         <v>10</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2227,7 +2209,7 @@
         <v>8</v>
       </c>
       <c r="Y19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z19">
         <v>8</v>
@@ -2236,7 +2218,7 @@
         <v>8</v>
       </c>
       <c r="AB19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC19">
         <v>10</v>
@@ -2268,25 +2250,25 @@
         <v>10</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2325,7 +2307,7 @@
         <v>8</v>
       </c>
       <c r="AB20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC20">
         <v>10</v>
@@ -2357,25 +2339,25 @@
         <v>6</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2399,10 +2381,10 @@
         <v>-1</v>
       </c>
       <c r="W21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y21">
         <v>7</v>
@@ -2414,10 +2396,10 @@
         <v>8</v>
       </c>
       <c r="AB21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC21">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2446,25 +2428,25 @@
         <v>8</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2491,22 +2473,22 @@
         <v>5</v>
       </c>
       <c r="X22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA22">
         <v>8</v>
       </c>
       <c r="AB22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC22">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2535,25 +2517,25 @@
         <v>7</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2583,7 +2565,7 @@
         <v>8</v>
       </c>
       <c r="Y23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z23">
         <v>7</v>
@@ -2595,7 +2577,7 @@
         <v>7</v>
       </c>
       <c r="AC23">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2624,25 +2606,25 @@
         <v>10</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2672,16 +2654,16 @@
         <v>9</v>
       </c>
       <c r="Y24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z24">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA24">
         <v>8</v>
       </c>
       <c r="AB24">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC24">
         <v>10</v>
@@ -2713,25 +2695,25 @@
         <v>9</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2761,7 +2743,7 @@
         <v>8</v>
       </c>
       <c r="Y25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z25">
         <v>10</v>
@@ -2770,10 +2752,10 @@
         <v>8</v>
       </c>
       <c r="AB25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC25">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -2802,25 +2784,25 @@
         <v>10</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -2859,7 +2841,7 @@
         <v>8</v>
       </c>
       <c r="AB26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC26">
         <v>10</v>
@@ -2891,25 +2873,25 @@
         <v>10</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -2933,7 +2915,7 @@
         <v>-1</v>
       </c>
       <c r="W27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X27">
         <v>9</v>
@@ -2948,7 +2930,7 @@
         <v>8</v>
       </c>
       <c r="AB27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC27">
         <v>10</v>
@@ -2980,25 +2962,25 @@
         <v>8</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -3022,13 +3004,13 @@
         <v>-1</v>
       </c>
       <c r="W28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X28">
         <v>8</v>
       </c>
       <c r="Y28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z28">
         <v>10</v>
@@ -3040,7 +3022,7 @@
         <v>8</v>
       </c>
       <c r="AC28">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -3069,25 +3051,25 @@
         <v>7</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -3120,16 +3102,16 @@
         <v>8</v>
       </c>
       <c r="Z29">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA29">
         <v>8</v>
       </c>
       <c r="AB29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC29">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3158,25 +3140,25 @@
         <v>10</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -3206,7 +3188,7 @@
         <v>8</v>
       </c>
       <c r="Y30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z30">
         <v>10</v>
@@ -3215,7 +3197,7 @@
         <v>8</v>
       </c>
       <c r="AB30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC30">
         <v>10</v>
@@ -3247,25 +3229,25 @@
         <v>10</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P31">
         <v>-1</v>
@@ -3289,13 +3271,13 @@
         <v>-1</v>
       </c>
       <c r="W31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X31">
         <v>9</v>
       </c>
       <c r="Y31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z31">
         <v>10</v>
@@ -3304,7 +3286,7 @@
         <v>8</v>
       </c>
       <c r="AB31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC31">
         <v>10</v>
@@ -3336,25 +3318,25 @@
         <v>7</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P32">
         <v>-1</v>
@@ -3384,7 +3366,7 @@
         <v>9</v>
       </c>
       <c r="Y32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z32">
         <v>7</v>
@@ -3393,10 +3375,10 @@
         <v>8</v>
       </c>
       <c r="AB32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC32">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3547,7 +3529,7 @@
         <v>100</v>
       </c>
       <c r="I4">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J4">
         <v>100</v>
@@ -3568,7 +3550,7 @@
         <v>100</v>
       </c>
       <c r="P4">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="Q4">
         <v>100</v>
@@ -3615,7 +3597,7 @@
         <v>100</v>
       </c>
       <c r="I5">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J5">
         <v>100</v>
@@ -3630,13 +3612,13 @@
         <v>100</v>
       </c>
       <c r="N5">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="O5">
         <v>100</v>
       </c>
       <c r="P5">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="Q5">
         <v>100</v>
@@ -3651,7 +3633,7 @@
         <v>100</v>
       </c>
       <c r="U5">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="V5">
         <v>100</v>
@@ -3698,7 +3680,7 @@
         <v>100</v>
       </c>
       <c r="N6">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="O6">
         <v>100</v>
@@ -3719,7 +3701,7 @@
         <v>100</v>
       </c>
       <c r="U6">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="V6">
         <v>100</v>
@@ -3766,7 +3748,7 @@
         <v>100</v>
       </c>
       <c r="N7">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="O7">
         <v>100</v>
@@ -3787,7 +3769,7 @@
         <v>100</v>
       </c>
       <c r="U7">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="V7">
         <v>100</v>
@@ -3819,7 +3801,7 @@
         <v>100</v>
       </c>
       <c r="I8">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J8">
         <v>100</v>
@@ -3834,13 +3816,13 @@
         <v>100</v>
       </c>
       <c r="N8">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="O8">
         <v>100</v>
       </c>
       <c r="P8">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="Q8">
         <v>100</v>
@@ -3855,7 +3837,7 @@
         <v>100</v>
       </c>
       <c r="U8">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="V8">
         <v>100</v>
@@ -3887,7 +3869,7 @@
         <v>100</v>
       </c>
       <c r="I9">
-        <v>75</v>
+        <v>82.5</v>
       </c>
       <c r="J9">
         <v>100</v>
@@ -3902,13 +3884,13 @@
         <v>100</v>
       </c>
       <c r="N9">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="O9">
         <v>100</v>
       </c>
       <c r="P9">
-        <v>75</v>
+        <v>82.5</v>
       </c>
       <c r="Q9">
         <v>100</v>
@@ -3923,7 +3905,7 @@
         <v>100</v>
       </c>
       <c r="U9">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="V9">
         <v>100</v>
@@ -3955,7 +3937,7 @@
         <v>100</v>
       </c>
       <c r="I10">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J10">
         <v>100</v>
@@ -3970,13 +3952,13 @@
         <v>100</v>
       </c>
       <c r="N10">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="O10">
         <v>100</v>
       </c>
       <c r="P10">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="Q10">
         <v>100</v>
@@ -3991,7 +3973,7 @@
         <v>100</v>
       </c>
       <c r="U10">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="V10">
         <v>100</v>
@@ -4023,7 +4005,7 @@
         <v>100</v>
       </c>
       <c r="I11">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J11">
         <v>100</v>
@@ -4038,13 +4020,13 @@
         <v>100</v>
       </c>
       <c r="N11">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="O11">
         <v>100</v>
       </c>
       <c r="P11">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="Q11">
         <v>100</v>
@@ -4059,7 +4041,7 @@
         <v>100</v>
       </c>
       <c r="U11">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="V11">
         <v>100</v>
@@ -4091,7 +4073,7 @@
         <v>100</v>
       </c>
       <c r="I12">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J12">
         <v>100</v>
@@ -4106,13 +4088,13 @@
         <v>100</v>
       </c>
       <c r="N12">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="O12">
         <v>100</v>
       </c>
       <c r="P12">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="Q12">
         <v>100</v>
@@ -4127,7 +4109,7 @@
         <v>100</v>
       </c>
       <c r="U12">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="V12">
         <v>100</v>
@@ -4174,7 +4156,7 @@
         <v>100</v>
       </c>
       <c r="N13">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="O13">
         <v>100</v>
@@ -4195,7 +4177,7 @@
         <v>100</v>
       </c>
       <c r="U13">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="V13">
         <v>100</v>
@@ -4227,7 +4209,7 @@
         <v>100</v>
       </c>
       <c r="I14">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J14">
         <v>100</v>
@@ -4242,13 +4224,13 @@
         <v>100</v>
       </c>
       <c r="N14">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="O14">
         <v>100</v>
       </c>
       <c r="P14">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="Q14">
         <v>100</v>
@@ -4263,7 +4245,7 @@
         <v>100</v>
       </c>
       <c r="U14">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="V14">
         <v>100</v>
@@ -4295,7 +4277,7 @@
         <v>100</v>
       </c>
       <c r="I15">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="J15">
         <v>100</v>
@@ -4310,13 +4292,13 @@
         <v>100</v>
       </c>
       <c r="N15">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="O15">
         <v>100</v>
       </c>
       <c r="P15">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="Q15">
         <v>100</v>
@@ -4331,7 +4313,7 @@
         <v>100</v>
       </c>
       <c r="U15">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="V15">
         <v>100</v>
@@ -4378,7 +4360,7 @@
         <v>100</v>
       </c>
       <c r="N16">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="O16">
         <v>100</v>
@@ -4399,7 +4381,7 @@
         <v>100</v>
       </c>
       <c r="U16">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="V16">
         <v>100</v>
@@ -4446,7 +4428,7 @@
         <v>100</v>
       </c>
       <c r="N17">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="O17">
         <v>100</v>
@@ -4467,7 +4449,7 @@
         <v>100</v>
       </c>
       <c r="U17">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="V17">
         <v>100</v>
@@ -4505,7 +4487,7 @@
         <v>100</v>
       </c>
       <c r="K18">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="L18">
         <v>100</v>
@@ -4514,7 +4496,7 @@
         <v>100</v>
       </c>
       <c r="N18">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="O18">
         <v>100</v>
@@ -4526,7 +4508,7 @@
         <v>100</v>
       </c>
       <c r="R18">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="S18">
         <v>100</v>
@@ -4535,7 +4517,7 @@
         <v>100</v>
       </c>
       <c r="U18">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="V18">
         <v>100</v>
@@ -4582,7 +4564,7 @@
         <v>100</v>
       </c>
       <c r="N19">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="O19">
         <v>100</v>
@@ -4603,7 +4585,7 @@
         <v>100</v>
       </c>
       <c r="U19">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="V19">
         <v>100</v>
@@ -4635,7 +4617,7 @@
         <v>100</v>
       </c>
       <c r="I20">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J20">
         <v>100</v>
@@ -4650,13 +4632,13 @@
         <v>100</v>
       </c>
       <c r="N20">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="O20">
         <v>100</v>
       </c>
       <c r="P20">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="Q20">
         <v>100</v>
@@ -4671,7 +4653,7 @@
         <v>100</v>
       </c>
       <c r="U20">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="V20">
         <v>100</v>
@@ -4703,7 +4685,7 @@
         <v>100</v>
       </c>
       <c r="I21">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J21">
         <v>100</v>
@@ -4718,13 +4700,13 @@
         <v>100</v>
       </c>
       <c r="N21">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="O21">
         <v>100</v>
       </c>
       <c r="P21">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="Q21">
         <v>100</v>
@@ -4739,7 +4721,7 @@
         <v>100</v>
       </c>
       <c r="U21">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="V21">
         <v>100</v>
@@ -4786,7 +4768,7 @@
         <v>100</v>
       </c>
       <c r="N22">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="O22">
         <v>100</v>
@@ -4807,7 +4789,7 @@
         <v>100</v>
       </c>
       <c r="U22">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="V22">
         <v>100</v>
@@ -4839,7 +4821,7 @@
         <v>100</v>
       </c>
       <c r="I23">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J23">
         <v>100</v>
@@ -4854,13 +4836,13 @@
         <v>100</v>
       </c>
       <c r="N23">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="O23">
         <v>100</v>
       </c>
       <c r="P23">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="Q23">
         <v>100</v>
@@ -4875,7 +4857,7 @@
         <v>100</v>
       </c>
       <c r="U23">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="V23">
         <v>100</v>
@@ -4907,7 +4889,7 @@
         <v>100</v>
       </c>
       <c r="I24">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="J24">
         <v>100</v>
@@ -4922,13 +4904,13 @@
         <v>100</v>
       </c>
       <c r="N24">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="O24">
         <v>100</v>
       </c>
       <c r="P24">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="Q24">
         <v>100</v>
@@ -4943,7 +4925,7 @@
         <v>100</v>
       </c>
       <c r="U24">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="V24">
         <v>100</v>
@@ -4990,7 +4972,7 @@
         <v>100</v>
       </c>
       <c r="N25">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="O25">
         <v>100</v>
@@ -5011,7 +4993,7 @@
         <v>100</v>
       </c>
       <c r="U25">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="V25">
         <v>100</v>
@@ -5058,7 +5040,7 @@
         <v>100</v>
       </c>
       <c r="N26">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="O26">
         <v>100</v>
@@ -5079,7 +5061,7 @@
         <v>100</v>
       </c>
       <c r="U26">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="V26">
         <v>100</v>
@@ -5126,7 +5108,7 @@
         <v>100</v>
       </c>
       <c r="N27">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="O27">
         <v>100</v>
@@ -5147,7 +5129,7 @@
         <v>100</v>
       </c>
       <c r="U27">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="V27">
         <v>100</v>
@@ -5194,7 +5176,7 @@
         <v>100</v>
       </c>
       <c r="N28">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="O28">
         <v>100</v>
@@ -5215,7 +5197,7 @@
         <v>100</v>
       </c>
       <c r="U28">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="V28">
         <v>100</v>
@@ -5247,7 +5229,7 @@
         <v>100</v>
       </c>
       <c r="I29">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J29">
         <v>100</v>
@@ -5262,13 +5244,13 @@
         <v>100</v>
       </c>
       <c r="N29">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="O29">
         <v>100</v>
       </c>
       <c r="P29">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="Q29">
         <v>100</v>
@@ -5283,7 +5265,7 @@
         <v>100</v>
       </c>
       <c r="U29">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="V29">
         <v>100</v>
@@ -5330,7 +5312,7 @@
         <v>100</v>
       </c>
       <c r="N30">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="O30">
         <v>100</v>
@@ -5351,7 +5333,7 @@
         <v>100</v>
       </c>
       <c r="U30">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="V30">
         <v>100</v>
@@ -5383,7 +5365,7 @@
         <v>100</v>
       </c>
       <c r="I31">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J31">
         <v>100</v>
@@ -5398,13 +5380,13 @@
         <v>100</v>
       </c>
       <c r="N31">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="O31">
         <v>100</v>
       </c>
       <c r="P31">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="Q31">
         <v>100</v>
@@ -5419,7 +5401,7 @@
         <v>100</v>
       </c>
       <c r="U31">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="V31">
         <v>100</v>
@@ -5451,7 +5433,7 @@
         <v>100</v>
       </c>
       <c r="I32">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J32">
         <v>100</v>
@@ -5466,13 +5448,13 @@
         <v>100</v>
       </c>
       <c r="N32">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="O32">
         <v>100</v>
       </c>
       <c r="P32">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="Q32">
         <v>100</v>
@@ -5487,7 +5469,7 @@
         <v>100</v>
       </c>
       <c r="U32">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="V32">
         <v>100</v>
@@ -5556,19 +5538,19 @@
         <v>29</v>
       </c>
       <c r="D2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F2" s="2">
-        <v>51.7</v>
+        <v>55.2</v>
       </c>
       <c r="G2" s="2">
-        <v>48.3</v>
+        <v>44.8</v>
       </c>
       <c r="H2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5588,19 +5570,19 @@
         <v>29</v>
       </c>
       <c r="D3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F3" s="2">
-        <v>82.8</v>
+        <v>86.2</v>
       </c>
       <c r="G3" s="2">
-        <v>17.2</v>
+        <v>13.8</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5620,16 +5602,16 @@
         <v>29</v>
       </c>
       <c r="D4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4" s="2">
-        <v>86.2</v>
+        <v>89.7</v>
       </c>
       <c r="G4" s="2">
-        <v>13.8</v>
+        <v>10.3</v>
       </c>
       <c r="H4">
         <v>7.8</v>
@@ -5643,7 +5625,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>57</v>
@@ -5652,19 +5634,19 @@
         <v>29</v>
       </c>
       <c r="D5">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2">
-        <v>96.59999999999999</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="G5" s="2">
-        <v>3.4</v>
+        <v>6.9</v>
       </c>
       <c r="H5">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5675,7 +5657,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
         <v>58</v>
@@ -5684,19 +5666,19 @@
         <v>29</v>
       </c>
       <c r="D6">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" s="2">
-        <v>96.59999999999999</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="G6" s="2">
-        <v>3.4</v>
+        <v>6.9</v>
       </c>
       <c r="H6">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5707,7 +5689,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
         <v>59</v>
@@ -5716,19 +5698,19 @@
         <v>29</v>
       </c>
       <c r="D7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2">
-        <v>96.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="G7" s="2">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5810,7 +5792,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5842,16 +5824,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920010</v>
+        <v>22330051920003</v>
       </c>
       <c r="B2" t="s">
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -5865,22 +5847,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920010</v>
+        <v>22330051920003</v>
       </c>
       <c r="B3" t="s">
         <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5888,16 +5870,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920013</v>
+        <v>22330051920010</v>
       </c>
       <c r="B4" t="s">
         <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D4" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -5911,22 +5893,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920013</v>
+        <v>22330051920010</v>
       </c>
       <c r="B5" t="s">
         <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D5" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5940,10 +5922,10 @@
         <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -5963,10 +5945,10 @@
         <v>67</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E7" t="s">
         <v>6</v>
@@ -5980,16 +5962,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920173</v>
+        <v>22330051920002</v>
       </c>
       <c r="B8" t="s">
         <v>68</v>
       </c>
       <c r="C8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D8" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
@@ -6003,22 +5985,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920173</v>
+        <v>22330051920015</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D9" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -6026,16 +6008,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920002</v>
+        <v>22330051920018</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D10" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
@@ -6049,16 +6031,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920005</v>
+        <v>22330051920012</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D11" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E11" t="s">
         <v>5</v>
@@ -6072,16 +6054,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920014</v>
+        <v>22330051920022</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D12" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E12" t="s">
         <v>5</v>
@@ -6095,16 +6077,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920018</v>
+        <v>22330051920322</v>
       </c>
       <c r="B13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D13" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E13" t="s">
         <v>5</v>
@@ -6118,16 +6100,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920012</v>
+        <v>22330051920173</v>
       </c>
       <c r="B14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D14" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E14" t="s">
         <v>5</v>
@@ -6136,75 +6118,6 @@
         <v>54</v>
       </c>
       <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>22330051920382</v>
-      </c>
-      <c r="B15" t="s">
-        <v>74</v>
-      </c>
-      <c r="C15" t="s">
-        <v>86</v>
-      </c>
-      <c r="D15" t="s">
-        <v>97</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>55</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>22330051920022</v>
-      </c>
-      <c r="B16" t="s">
-        <v>75</v>
-      </c>
-      <c r="C16" t="s">
-        <v>85</v>
-      </c>
-      <c r="D16" t="s">
-        <v>98</v>
-      </c>
-      <c r="E16" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" t="s">
-        <v>54</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>22330051920322</v>
-      </c>
-      <c r="B17" t="s">
-        <v>76</v>
-      </c>
-      <c r="C17" t="s">
-        <v>87</v>
-      </c>
-      <c r="D17" t="s">
-        <v>99</v>
-      </c>
-      <c r="E17" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" t="s">
-        <v>54</v>
-      </c>
-      <c r="G17">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4AEM - Estadisticos 20232.xlsx
+++ b/grupos/4AEM - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="130">
   <si>
     <t>Materia</t>
   </si>
@@ -182,24 +182,24 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Faltante Faltante Faltante</t>
+  </si>
+  <si>
+    <t>Rivera Cruz Ezequiel</t>
+  </si>
+  <si>
+    <t>Jiménez Nieto Enrique</t>
+  </si>
+  <si>
     <t>Sanchez Morales Gilberto</t>
   </si>
   <si>
+    <t>Hernández Castro Enrique</t>
+  </si>
+  <si>
     <t>Avila Coronado Julieta</t>
   </si>
   <si>
-    <t>Rivera Cruz Ezequiel</t>
-  </si>
-  <si>
-    <t>Faltante Faltante Faltante</t>
-  </si>
-  <si>
-    <t>Jiménez Nieto Enrique</t>
-  </si>
-  <si>
-    <t>Hernández Castro Enrique</t>
-  </si>
-  <si>
     <t>Cruz Alejo José Armando</t>
   </si>
   <si>
@@ -218,16 +218,31 @@
     <t>APALE</t>
   </si>
   <si>
-    <t>CRUZ</t>
+    <t>GARCIA</t>
   </si>
   <si>
     <t>GUERRA</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>ALVAREZ</t>
   </si>
   <si>
-    <t>GARCIA</t>
+    <t>ARGUELLES</t>
+  </si>
+  <si>
+    <t>BASILIO</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
   </si>
   <si>
     <t>HERRERA</t>
@@ -242,49 +257,115 @@
     <t>PANZO</t>
   </si>
   <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>RIOS</t>
+  </si>
+  <si>
     <t>ROMERO</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>TREJO</t>
+  </si>
+  <si>
     <t>TEXOCO</t>
   </si>
   <si>
-    <t>COYOHUA</t>
+    <t>QUERO</t>
   </si>
   <si>
     <t>JERONIMO</t>
   </si>
   <si>
+    <t>ZARATE</t>
+  </si>
+  <si>
     <t>ROSAS</t>
   </si>
   <si>
-    <t>QUERO</t>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>ANGEL</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
   </si>
   <si>
     <t>AVELINO</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
+    <t>RODRIGUEZ</t>
   </si>
   <si>
     <t>MACARIO</t>
   </si>
   <si>
-    <t>RAMOS</t>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>GALVAN</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>GILES</t>
+  </si>
+  <si>
+    <t>CERVANTES</t>
   </si>
   <si>
     <t>DANIEL</t>
   </si>
   <si>
-    <t>DIEGO</t>
+    <t>DIEGO JESUS</t>
   </si>
   <si>
     <t>LUIS</t>
   </si>
   <si>
+    <t>OSMAR UZIEL</t>
+  </si>
+  <si>
     <t>RUBEN DE JESUS</t>
   </si>
   <si>
-    <t>DIEGO JESUS</t>
+    <t>RICARDO</t>
+  </si>
+  <si>
+    <t>LUIS FERNANDO</t>
+  </si>
+  <si>
+    <t>CRISTHIAN</t>
+  </si>
+  <si>
+    <t>ISABEL</t>
+  </si>
+  <si>
+    <t>JESUS YAEL</t>
+  </si>
+  <si>
+    <t>GABAEL</t>
   </si>
   <si>
     <t>KEVIN</t>
@@ -293,13 +374,40 @@
     <t>ALEXANDER</t>
   </si>
   <si>
+    <t>RAFAEL</t>
+  </si>
+  <si>
     <t>CESAR</t>
   </si>
   <si>
     <t>SHERLIN</t>
   </si>
   <si>
+    <t>VALENTINA</t>
+  </si>
+  <si>
+    <t>DYLAN OSMAR</t>
+  </si>
+  <si>
+    <t>GABRIEL</t>
+  </si>
+  <si>
+    <t>GREGORIO</t>
+  </si>
+  <si>
+    <t>SAUL AZAEL</t>
+  </si>
+  <si>
     <t>ANGEL GUILLERMO</t>
+  </si>
+  <si>
+    <t>FERNANDO</t>
+  </si>
+  <si>
+    <t>ISAAC JOHAMET</t>
+  </si>
+  <si>
+    <t>CHRISTOPHER ANDRUS</t>
   </si>
 </sst>
 </file>
@@ -847,22 +955,22 @@
         <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V4">
         <v>-1</v>
@@ -936,28 +1044,28 @@
         <v>7</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V5">
         <v>-1</v>
       </c>
       <c r="W5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X5">
         <v>8</v>
@@ -972,7 +1080,7 @@
         <v>8</v>
       </c>
       <c r="AB5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AC5">
         <v>9</v>
@@ -1025,43 +1133,43 @@
         <v>6</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V6">
         <v>-1</v>
       </c>
       <c r="W6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y6">
         <v>8</v>
       </c>
       <c r="Z6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA6">
         <v>8</v>
       </c>
       <c r="AB6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AC6">
         <v>7</v>
@@ -1114,22 +1222,22 @@
         <v>10</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V7">
         <v>-1</v>
@@ -1150,7 +1258,7 @@
         <v>8</v>
       </c>
       <c r="AB7">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AC7">
         <v>10</v>
@@ -1203,22 +1311,22 @@
         <v>6</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V8">
         <v>-1</v>
@@ -1239,7 +1347,7 @@
         <v>8</v>
       </c>
       <c r="AB8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AC8">
         <v>8</v>
@@ -1292,28 +1400,28 @@
         <v>5</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V9">
         <v>-1</v>
       </c>
       <c r="W9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X9">
         <v>5</v>
@@ -1322,7 +1430,7 @@
         <v>6</v>
       </c>
       <c r="Z9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA9">
         <v>8</v>
@@ -1369,7 +1477,7 @@
         <v>10</v>
       </c>
       <c r="L10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M10">
         <v>8</v>
@@ -1381,22 +1489,22 @@
         <v>9</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V10">
         <v>-1</v>
@@ -1405,19 +1513,19 @@
         <v>7</v>
       </c>
       <c r="X10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y10">
         <v>10</v>
       </c>
       <c r="Z10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA10">
         <v>8</v>
       </c>
       <c r="AB10">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AC10">
         <v>10</v>
@@ -1470,22 +1578,22 @@
         <v>9</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V11">
         <v>-1</v>
@@ -1506,7 +1614,7 @@
         <v>8</v>
       </c>
       <c r="AB11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC11">
         <v>8</v>
@@ -1559,28 +1667,28 @@
         <v>10</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V12">
         <v>-1</v>
       </c>
       <c r="W12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X12">
         <v>8</v>
@@ -1592,10 +1700,10 @@
         <v>9</v>
       </c>
       <c r="AA12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB12">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AC12">
         <v>10</v>
@@ -1648,37 +1756,37 @@
         <v>6</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V13">
         <v>-1</v>
       </c>
       <c r="W13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y13">
         <v>7</v>
       </c>
       <c r="Z13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA13">
         <v>8</v>
@@ -1737,22 +1845,22 @@
         <v>9</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V14">
         <v>-1</v>
@@ -1761,19 +1869,19 @@
         <v>7</v>
       </c>
       <c r="X14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y14">
         <v>9</v>
       </c>
       <c r="Z14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA14">
         <v>8</v>
       </c>
       <c r="AB14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AC14">
         <v>9</v>
@@ -1826,31 +1934,31 @@
         <v>8</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V15">
         <v>-1</v>
       </c>
       <c r="W15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y15">
         <v>9</v>
@@ -1862,7 +1970,7 @@
         <v>8</v>
       </c>
       <c r="AB15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AC15">
         <v>8</v>
@@ -1915,22 +2023,22 @@
         <v>6</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V16">
         <v>-1</v>
@@ -1945,13 +2053,13 @@
         <v>8</v>
       </c>
       <c r="Z16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA16">
         <v>8</v>
       </c>
       <c r="AB16">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AC16">
         <v>8</v>
@@ -2004,22 +2112,22 @@
         <v>10</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V17">
         <v>-1</v>
@@ -2028,7 +2136,7 @@
         <v>8</v>
       </c>
       <c r="X17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y17">
         <v>10</v>
@@ -2040,7 +2148,7 @@
         <v>8</v>
       </c>
       <c r="AB17">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AC17">
         <v>10</v>
@@ -2093,28 +2201,28 @@
         <v>5</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V18">
         <v>-1</v>
       </c>
       <c r="W18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X18">
         <v>5</v>
@@ -2129,7 +2237,7 @@
         <v>8</v>
       </c>
       <c r="AB18">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AC18">
         <v>7</v>
@@ -2182,34 +2290,34 @@
         <v>9</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V19">
         <v>-1</v>
       </c>
       <c r="W19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X19">
         <v>8</v>
       </c>
       <c r="Y19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z19">
         <v>8</v>
@@ -2218,7 +2326,7 @@
         <v>8</v>
       </c>
       <c r="AB19">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AC19">
         <v>10</v>
@@ -2271,22 +2379,22 @@
         <v>10</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V20">
         <v>-1</v>
@@ -2304,10 +2412,10 @@
         <v>10</v>
       </c>
       <c r="AA20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB20">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AC20">
         <v>10</v>
@@ -2360,28 +2468,28 @@
         <v>5</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V21">
         <v>-1</v>
       </c>
       <c r="W21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X21">
         <v>6</v>
@@ -2390,13 +2498,13 @@
         <v>7</v>
       </c>
       <c r="Z21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA21">
         <v>8</v>
       </c>
       <c r="AB21">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AC21">
         <v>5</v>
@@ -2449,31 +2557,31 @@
         <v>6</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V22">
         <v>-1</v>
       </c>
       <c r="W22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y22">
         <v>8</v>
@@ -2485,7 +2593,7 @@
         <v>8</v>
       </c>
       <c r="AB22">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AC22">
         <v>7</v>
@@ -2538,43 +2646,43 @@
         <v>8</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V23">
         <v>-1</v>
       </c>
       <c r="W23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA23">
         <v>8</v>
       </c>
       <c r="AB23">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AC23">
         <v>8</v>
@@ -2627,31 +2735,31 @@
         <v>10</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V24">
         <v>-1</v>
       </c>
       <c r="W24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y24">
         <v>10</v>
@@ -2663,7 +2771,7 @@
         <v>8</v>
       </c>
       <c r="AB24">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AC24">
         <v>10</v>
@@ -2716,22 +2824,22 @@
         <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V25">
         <v>-1</v>
@@ -2752,7 +2860,7 @@
         <v>8</v>
       </c>
       <c r="AB25">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AC25">
         <v>10</v>
@@ -2805,22 +2913,22 @@
         <v>10</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V26">
         <v>-1</v>
@@ -2841,7 +2949,7 @@
         <v>8</v>
       </c>
       <c r="AB26">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AC26">
         <v>10</v>
@@ -2894,22 +3002,22 @@
         <v>9</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V27">
         <v>-1</v>
@@ -2930,7 +3038,7 @@
         <v>8</v>
       </c>
       <c r="AB27">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AC27">
         <v>10</v>
@@ -2983,22 +3091,22 @@
         <v>9</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V28">
         <v>-1</v>
@@ -3019,7 +3127,7 @@
         <v>8</v>
       </c>
       <c r="AB28">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AC28">
         <v>9</v>
@@ -3072,34 +3180,34 @@
         <v>5</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V29">
         <v>-1</v>
       </c>
       <c r="W29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z29">
         <v>7</v>
@@ -3108,7 +3216,7 @@
         <v>8</v>
       </c>
       <c r="AB29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC29">
         <v>6</v>
@@ -3161,22 +3269,22 @@
         <v>10</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V30">
         <v>-1</v>
@@ -3188,7 +3296,7 @@
         <v>8</v>
       </c>
       <c r="Y30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z30">
         <v>10</v>
@@ -3197,7 +3305,7 @@
         <v>8</v>
       </c>
       <c r="AB30">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AC30">
         <v>10</v>
@@ -3250,22 +3358,22 @@
         <v>10</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V31">
         <v>-1</v>
@@ -3286,7 +3394,7 @@
         <v>8</v>
       </c>
       <c r="AB31">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AC31">
         <v>10</v>
@@ -3339,22 +3447,22 @@
         <v>9</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V32">
         <v>-1</v>
@@ -3369,13 +3477,13 @@
         <v>9</v>
       </c>
       <c r="Z32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA32">
         <v>8</v>
       </c>
       <c r="AB32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC32">
         <v>8</v>
@@ -3550,7 +3658,7 @@
         <v>100</v>
       </c>
       <c r="P4">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q4">
         <v>100</v>
@@ -3618,7 +3726,7 @@
         <v>100</v>
       </c>
       <c r="P5">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q5">
         <v>100</v>
@@ -3633,7 +3741,7 @@
         <v>100</v>
       </c>
       <c r="U5">
-        <v>68.8</v>
+        <v>76.2</v>
       </c>
       <c r="V5">
         <v>100</v>
@@ -3701,7 +3809,7 @@
         <v>100</v>
       </c>
       <c r="U6">
-        <v>68.8</v>
+        <v>76.2</v>
       </c>
       <c r="V6">
         <v>100</v>
@@ -3769,7 +3877,7 @@
         <v>100</v>
       </c>
       <c r="U7">
-        <v>68.8</v>
+        <v>76.2</v>
       </c>
       <c r="V7">
         <v>100</v>
@@ -3822,7 +3930,7 @@
         <v>100</v>
       </c>
       <c r="P8">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q8">
         <v>100</v>
@@ -3837,7 +3945,7 @@
         <v>100</v>
       </c>
       <c r="U8">
-        <v>68.8</v>
+        <v>76.2</v>
       </c>
       <c r="V8">
         <v>100</v>
@@ -3890,7 +3998,7 @@
         <v>100</v>
       </c>
       <c r="P9">
-        <v>82.5</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="Q9">
         <v>100</v>
@@ -3905,7 +4013,7 @@
         <v>100</v>
       </c>
       <c r="U9">
-        <v>68.8</v>
+        <v>76.2</v>
       </c>
       <c r="V9">
         <v>100</v>
@@ -3958,7 +4066,7 @@
         <v>100</v>
       </c>
       <c r="P10">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q10">
         <v>100</v>
@@ -3973,7 +4081,7 @@
         <v>100</v>
       </c>
       <c r="U10">
-        <v>68.8</v>
+        <v>76.2</v>
       </c>
       <c r="V10">
         <v>100</v>
@@ -4026,7 +4134,7 @@
         <v>100</v>
       </c>
       <c r="P11">
-        <v>95</v>
+        <v>95.3</v>
       </c>
       <c r="Q11">
         <v>100</v>
@@ -4041,7 +4149,7 @@
         <v>100</v>
       </c>
       <c r="U11">
-        <v>68.8</v>
+        <v>76.2</v>
       </c>
       <c r="V11">
         <v>100</v>
@@ -4094,7 +4202,7 @@
         <v>100</v>
       </c>
       <c r="P12">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q12">
         <v>100</v>
@@ -4109,7 +4217,7 @@
         <v>100</v>
       </c>
       <c r="U12">
-        <v>68.8</v>
+        <v>76.2</v>
       </c>
       <c r="V12">
         <v>100</v>
@@ -4162,7 +4270,7 @@
         <v>100</v>
       </c>
       <c r="P13">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q13">
         <v>100</v>
@@ -4177,7 +4285,7 @@
         <v>100</v>
       </c>
       <c r="U13">
-        <v>68.8</v>
+        <v>76.2</v>
       </c>
       <c r="V13">
         <v>100</v>
@@ -4230,7 +4338,7 @@
         <v>100</v>
       </c>
       <c r="P14">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q14">
         <v>100</v>
@@ -4245,7 +4353,7 @@
         <v>100</v>
       </c>
       <c r="U14">
-        <v>68.8</v>
+        <v>76.2</v>
       </c>
       <c r="V14">
         <v>100</v>
@@ -4298,7 +4406,7 @@
         <v>100</v>
       </c>
       <c r="P15">
-        <v>90</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q15">
         <v>100</v>
@@ -4313,7 +4421,7 @@
         <v>100</v>
       </c>
       <c r="U15">
-        <v>68.8</v>
+        <v>76.2</v>
       </c>
       <c r="V15">
         <v>100</v>
@@ -4381,7 +4489,7 @@
         <v>100</v>
       </c>
       <c r="U16">
-        <v>68.8</v>
+        <v>76.2</v>
       </c>
       <c r="V16">
         <v>100</v>
@@ -4449,7 +4557,7 @@
         <v>100</v>
       </c>
       <c r="U17">
-        <v>68.8</v>
+        <v>76.2</v>
       </c>
       <c r="V17">
         <v>100</v>
@@ -4502,13 +4610,13 @@
         <v>100</v>
       </c>
       <c r="P18">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="Q18">
         <v>100</v>
       </c>
       <c r="R18">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S18">
         <v>100</v>
@@ -4517,7 +4625,7 @@
         <v>100</v>
       </c>
       <c r="U18">
-        <v>68.8</v>
+        <v>76.2</v>
       </c>
       <c r="V18">
         <v>100</v>
@@ -4585,7 +4693,7 @@
         <v>100</v>
       </c>
       <c r="U19">
-        <v>68.8</v>
+        <v>76.2</v>
       </c>
       <c r="V19">
         <v>100</v>
@@ -4638,7 +4746,7 @@
         <v>100</v>
       </c>
       <c r="P20">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q20">
         <v>100</v>
@@ -4653,7 +4761,7 @@
         <v>100</v>
       </c>
       <c r="U20">
-        <v>68.8</v>
+        <v>76.2</v>
       </c>
       <c r="V20">
         <v>100</v>
@@ -4706,7 +4814,7 @@
         <v>100</v>
       </c>
       <c r="P21">
-        <v>95</v>
+        <v>92.2</v>
       </c>
       <c r="Q21">
         <v>100</v>
@@ -4721,7 +4829,7 @@
         <v>100</v>
       </c>
       <c r="U21">
-        <v>68.8</v>
+        <v>76.2</v>
       </c>
       <c r="V21">
         <v>100</v>
@@ -4789,7 +4897,7 @@
         <v>100</v>
       </c>
       <c r="U22">
-        <v>68.8</v>
+        <v>76.2</v>
       </c>
       <c r="V22">
         <v>100</v>
@@ -4842,7 +4950,7 @@
         <v>100</v>
       </c>
       <c r="P23">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q23">
         <v>100</v>
@@ -4857,7 +4965,7 @@
         <v>100</v>
       </c>
       <c r="U23">
-        <v>68.8</v>
+        <v>76.2</v>
       </c>
       <c r="V23">
         <v>100</v>
@@ -4910,7 +5018,7 @@
         <v>100</v>
       </c>
       <c r="P24">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
       <c r="Q24">
         <v>100</v>
@@ -4925,7 +5033,7 @@
         <v>100</v>
       </c>
       <c r="U24">
-        <v>68.8</v>
+        <v>76.2</v>
       </c>
       <c r="V24">
         <v>100</v>
@@ -4993,7 +5101,7 @@
         <v>100</v>
       </c>
       <c r="U25">
-        <v>68.8</v>
+        <v>76.2</v>
       </c>
       <c r="V25">
         <v>100</v>
@@ -5061,7 +5169,7 @@
         <v>100</v>
       </c>
       <c r="U26">
-        <v>68.8</v>
+        <v>76.2</v>
       </c>
       <c r="V26">
         <v>100</v>
@@ -5129,7 +5237,7 @@
         <v>100</v>
       </c>
       <c r="U27">
-        <v>68.8</v>
+        <v>76.2</v>
       </c>
       <c r="V27">
         <v>100</v>
@@ -5197,7 +5305,7 @@
         <v>100</v>
       </c>
       <c r="U28">
-        <v>68.8</v>
+        <v>76.2</v>
       </c>
       <c r="V28">
         <v>100</v>
@@ -5250,7 +5358,7 @@
         <v>100</v>
       </c>
       <c r="P29">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q29">
         <v>100</v>
@@ -5265,7 +5373,7 @@
         <v>100</v>
       </c>
       <c r="U29">
-        <v>68.8</v>
+        <v>76.2</v>
       </c>
       <c r="V29">
         <v>100</v>
@@ -5333,7 +5441,7 @@
         <v>100</v>
       </c>
       <c r="U30">
-        <v>68.8</v>
+        <v>76.2</v>
       </c>
       <c r="V30">
         <v>100</v>
@@ -5386,7 +5494,7 @@
         <v>100</v>
       </c>
       <c r="P31">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q31">
         <v>100</v>
@@ -5401,7 +5509,7 @@
         <v>100</v>
       </c>
       <c r="U31">
-        <v>68.8</v>
+        <v>76.2</v>
       </c>
       <c r="V31">
         <v>100</v>
@@ -5454,7 +5562,7 @@
         <v>100</v>
       </c>
       <c r="P32">
-        <v>97.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q32">
         <v>100</v>
@@ -5469,7 +5577,7 @@
         <v>100</v>
       </c>
       <c r="U32">
-        <v>68.8</v>
+        <v>76.2</v>
       </c>
       <c r="V32">
         <v>100</v>
@@ -5529,7 +5637,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>54</v>
@@ -5538,19 +5646,19 @@
         <v>29</v>
       </c>
       <c r="D2">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F2" s="2">
-        <v>55.2</v>
+        <v>3.4</v>
       </c>
       <c r="G2" s="2">
-        <v>44.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="H2">
-        <v>6.4</v>
+        <v>5.2</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5561,7 +5669,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>55</v>
@@ -5570,19 +5678,19 @@
         <v>29</v>
       </c>
       <c r="D3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3" s="2">
-        <v>86.2</v>
+        <v>82.8</v>
       </c>
       <c r="G3" s="2">
-        <v>13.8</v>
+        <v>17.2</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>7.6</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5593,7 +5701,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
         <v>56</v>
@@ -5602,19 +5710,19 @@
         <v>29</v>
       </c>
       <c r="D4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4" s="2">
-        <v>89.7</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="G4" s="2">
-        <v>10.3</v>
+        <v>6.9</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5625,7 +5733,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>57</v>
@@ -5634,19 +5742,19 @@
         <v>29</v>
       </c>
       <c r="D5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2">
-        <v>93.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="G5" s="2">
-        <v>6.9</v>
+        <v>3.4</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5657,7 +5765,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>58</v>
@@ -5666,16 +5774,16 @@
         <v>29</v>
       </c>
       <c r="D6">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2">
-        <v>93.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="G6" s="2">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="H6">
         <v>8.6</v>
@@ -5689,7 +5797,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>59</v>
@@ -5710,7 +5818,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5742,7 +5850,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -5792,7 +5900,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5830,16 +5938,16 @@
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5853,16 +5961,16 @@
         <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5870,22 +5978,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920010</v>
+        <v>22330051920015</v>
       </c>
       <c r="B4" t="s">
         <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="D4" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5893,22 +6001,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920010</v>
+        <v>22330051920015</v>
       </c>
       <c r="B5" t="s">
         <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="D5" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5922,16 +6030,16 @@
         <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="D6" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5945,16 +6053,16 @@
         <v>67</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="D7" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5962,19 +6070,19 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920002</v>
+        <v>22330051920382</v>
       </c>
       <c r="B8" t="s">
         <v>68</v>
       </c>
       <c r="C8" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="D8" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
         <v>54</v>
@@ -5985,22 +6093,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920015</v>
+        <v>22330051920382</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="D9" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="E9" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -6008,19 +6116,19 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920018</v>
+        <v>22330051920002</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C10" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="D10" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
         <v>54</v>
@@ -6031,19 +6139,19 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920012</v>
+        <v>22330051920004</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C11" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="D11" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E11" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
         <v>54</v>
@@ -6054,19 +6162,19 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920022</v>
+        <v>22330051920005</v>
       </c>
       <c r="B12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C12" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="D12" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
         <v>54</v>
@@ -6077,19 +6185,19 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920322</v>
+        <v>22330051920009</v>
       </c>
       <c r="B13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C13" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="D13" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="E13" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
         <v>54</v>
@@ -6100,24 +6208,415 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920173</v>
+        <v>22330051920013</v>
       </c>
       <c r="B14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="D14" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="E14" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
         <v>54</v>
       </c>
       <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>22330051920014</v>
+      </c>
+      <c r="B15" t="s">
+        <v>66</v>
+      </c>
+      <c r="C15" t="s">
+        <v>94</v>
+      </c>
+      <c r="D15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>22330051920016</v>
+      </c>
+      <c r="B16" t="s">
+        <v>74</v>
+      </c>
+      <c r="C16" t="s">
+        <v>95</v>
+      </c>
+      <c r="D16" t="s">
+        <v>114</v>
+      </c>
+      <c r="E16" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" t="s">
+        <v>54</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>22330051920320</v>
+      </c>
+      <c r="B17" t="s">
+        <v>74</v>
+      </c>
+      <c r="C17" t="s">
+        <v>96</v>
+      </c>
+      <c r="D17" t="s">
+        <v>115</v>
+      </c>
+      <c r="E17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" t="s">
+        <v>54</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>22330051920018</v>
+      </c>
+      <c r="B18" t="s">
+        <v>75</v>
+      </c>
+      <c r="C18" t="s">
+        <v>97</v>
+      </c>
+      <c r="D18" t="s">
+        <v>116</v>
+      </c>
+      <c r="E18" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" t="s">
+        <v>54</v>
+      </c>
+      <c r="G18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>22330051920012</v>
+      </c>
+      <c r="B19" t="s">
+        <v>76</v>
+      </c>
+      <c r="C19" t="s">
+        <v>83</v>
+      </c>
+      <c r="D19" t="s">
+        <v>117</v>
+      </c>
+      <c r="E19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>22330051920020</v>
+      </c>
+      <c r="B20" t="s">
+        <v>68</v>
+      </c>
+      <c r="C20" t="s">
+        <v>98</v>
+      </c>
+      <c r="D20" t="s">
+        <v>118</v>
+      </c>
+      <c r="E20" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" t="s">
+        <v>54</v>
+      </c>
+      <c r="G20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>22330051920022</v>
+      </c>
+      <c r="B21" t="s">
+        <v>77</v>
+      </c>
+      <c r="C21" t="s">
+        <v>83</v>
+      </c>
+      <c r="D21" t="s">
+        <v>119</v>
+      </c>
+      <c r="E21" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" t="s">
+        <v>54</v>
+      </c>
+      <c r="G21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>22330051920322</v>
+      </c>
+      <c r="B22" t="s">
+        <v>78</v>
+      </c>
+      <c r="C22" t="s">
+        <v>99</v>
+      </c>
+      <c r="D22" t="s">
+        <v>120</v>
+      </c>
+      <c r="E22" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" t="s">
+        <v>54</v>
+      </c>
+      <c r="G22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>22330051920023</v>
+      </c>
+      <c r="B23" t="s">
+        <v>79</v>
+      </c>
+      <c r="C23" t="s">
+        <v>100</v>
+      </c>
+      <c r="D23" t="s">
+        <v>121</v>
+      </c>
+      <c r="E23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" t="s">
+        <v>54</v>
+      </c>
+      <c r="G23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>22330051920024</v>
+      </c>
+      <c r="B24" t="s">
+        <v>80</v>
+      </c>
+      <c r="C24" t="s">
+        <v>92</v>
+      </c>
+      <c r="D24" t="s">
+        <v>122</v>
+      </c>
+      <c r="E24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" t="s">
+        <v>54</v>
+      </c>
+      <c r="G24">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>22330051920025</v>
+      </c>
+      <c r="B25" t="s">
+        <v>81</v>
+      </c>
+      <c r="C25" t="s">
+        <v>101</v>
+      </c>
+      <c r="D25" t="s">
+        <v>123</v>
+      </c>
+      <c r="E25" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" t="s">
+        <v>54</v>
+      </c>
+      <c r="G25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>22330051920326</v>
+      </c>
+      <c r="B26" t="s">
+        <v>82</v>
+      </c>
+      <c r="C26" t="s">
+        <v>102</v>
+      </c>
+      <c r="D26" t="s">
+        <v>124</v>
+      </c>
+      <c r="E26" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" t="s">
+        <v>54</v>
+      </c>
+      <c r="G26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>22330051920026</v>
+      </c>
+      <c r="B27" t="s">
+        <v>82</v>
+      </c>
+      <c r="C27" t="s">
+        <v>103</v>
+      </c>
+      <c r="D27" t="s">
+        <v>125</v>
+      </c>
+      <c r="E27" t="s">
+        <v>10</v>
+      </c>
+      <c r="F27" t="s">
+        <v>54</v>
+      </c>
+      <c r="G27">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>22330051920173</v>
+      </c>
+      <c r="B28" t="s">
+        <v>82</v>
+      </c>
+      <c r="C28" t="s">
+        <v>80</v>
+      </c>
+      <c r="D28" t="s">
+        <v>126</v>
+      </c>
+      <c r="E28" t="s">
+        <v>10</v>
+      </c>
+      <c r="F28" t="s">
+        <v>54</v>
+      </c>
+      <c r="G28">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>22330051920330</v>
+      </c>
+      <c r="B29" t="s">
+        <v>82</v>
+      </c>
+      <c r="C29" t="s">
+        <v>83</v>
+      </c>
+      <c r="D29" t="s">
+        <v>127</v>
+      </c>
+      <c r="E29" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29" t="s">
+        <v>54</v>
+      </c>
+      <c r="G29">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>22330051920027</v>
+      </c>
+      <c r="B30" t="s">
+        <v>83</v>
+      </c>
+      <c r="C30" t="s">
+        <v>104</v>
+      </c>
+      <c r="D30" t="s">
+        <v>128</v>
+      </c>
+      <c r="E30" t="s">
+        <v>10</v>
+      </c>
+      <c r="F30" t="s">
+        <v>54</v>
+      </c>
+      <c r="G30">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>22330051920332</v>
+      </c>
+      <c r="B31" t="s">
+        <v>84</v>
+      </c>
+      <c r="C31" t="s">
+        <v>68</v>
+      </c>
+      <c r="D31" t="s">
+        <v>129</v>
+      </c>
+      <c r="E31" t="s">
+        <v>10</v>
+      </c>
+      <c r="F31" t="s">
+        <v>54</v>
+      </c>
+      <c r="G31">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4AEM - Estadisticos 20232.xlsx
+++ b/grupos/4AEM - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="133">
   <si>
     <t>Materia</t>
   </si>
@@ -188,21 +188,21 @@
     <t>Rivera Cruz Ezequiel</t>
   </si>
   <si>
+    <t>Sanchez Morales Gilberto</t>
+  </si>
+  <si>
+    <t>Hernández Castro Enrique</t>
+  </si>
+  <si>
+    <t>Avila Coronado Julieta</t>
+  </si>
+  <si>
+    <t>Cruz Alejo José Armando</t>
+  </si>
+  <si>
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
-    <t>Sanchez Morales Gilberto</t>
-  </si>
-  <si>
-    <t>Hernández Castro Enrique</t>
-  </si>
-  <si>
-    <t>Avila Coronado Julieta</t>
-  </si>
-  <si>
-    <t>Cruz Alejo José Armando</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -218,39 +218,42 @@
     <t>APALE</t>
   </si>
   <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
     <t>GARCIA</t>
   </si>
   <si>
     <t>GUERRA</t>
   </si>
   <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>ARGUELLES</t>
+  </si>
+  <si>
+    <t>BASILIO</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>ARGUELLES</t>
-  </si>
-  <si>
-    <t>BASILIO</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
     <t>MERINO</t>
   </si>
   <si>
@@ -278,45 +281,48 @@
     <t>TEXOCO</t>
   </si>
   <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
     <t>QUERO</t>
   </si>
   <si>
     <t>JERONIMO</t>
   </si>
   <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>ANGEL</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>AVELINO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>ZARATE</t>
   </si>
   <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>ANGEL</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>AVELINO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
     <t>MACARIO</t>
   </si>
   <si>
@@ -338,43 +344,46 @@
     <t>DANIEL</t>
   </si>
   <si>
+    <t>EDER</t>
+  </si>
+  <si>
     <t>DIEGO JESUS</t>
   </si>
   <si>
     <t>LUIS</t>
   </si>
   <si>
+    <t>RUBEN DE JESUS</t>
+  </si>
+  <si>
+    <t>RICARDO</t>
+  </si>
+  <si>
+    <t>LUIS FERNANDO</t>
+  </si>
+  <si>
+    <t>CRISTHIAN</t>
+  </si>
+  <si>
+    <t>ISABEL</t>
+  </si>
+  <si>
+    <t>JESUS YAEL</t>
+  </si>
+  <si>
+    <t>GABAEL</t>
+  </si>
+  <si>
+    <t>KEVIN</t>
+  </si>
+  <si>
+    <t>ALEXANDER</t>
+  </si>
+  <si>
+    <t>RAFAEL</t>
+  </si>
+  <si>
     <t>OSMAR UZIEL</t>
-  </si>
-  <si>
-    <t>RUBEN DE JESUS</t>
-  </si>
-  <si>
-    <t>RICARDO</t>
-  </si>
-  <si>
-    <t>LUIS FERNANDO</t>
-  </si>
-  <si>
-    <t>CRISTHIAN</t>
-  </si>
-  <si>
-    <t>ISABEL</t>
-  </si>
-  <si>
-    <t>JESUS YAEL</t>
-  </si>
-  <si>
-    <t>GABAEL</t>
-  </si>
-  <si>
-    <t>KEVIN</t>
-  </si>
-  <si>
-    <t>ALEXANDER</t>
-  </si>
-  <si>
-    <t>RAFAEL</t>
   </si>
   <si>
     <t>CESAR</t>
@@ -973,7 +982,7 @@
         <v>10</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W4">
         <v>10</v>
@@ -1062,7 +1071,7 @@
         <v>6</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W5">
         <v>6</v>
@@ -1083,7 +1092,7 @@
         <v>5</v>
       </c>
       <c r="AC5">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -1151,7 +1160,7 @@
         <v>6</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W6">
         <v>6</v>
@@ -1240,7 +1249,7 @@
         <v>8</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W7">
         <v>8</v>
@@ -1329,7 +1338,7 @@
         <v>6</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W8">
         <v>6</v>
@@ -1418,7 +1427,7 @@
         <v>5</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W9">
         <v>6</v>
@@ -1439,7 +1448,7 @@
         <v>5</v>
       </c>
       <c r="AC9">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1507,7 +1516,7 @@
         <v>6</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W10">
         <v>7</v>
@@ -1528,7 +1537,7 @@
         <v>5</v>
       </c>
       <c r="AC10">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1596,7 +1605,7 @@
         <v>6</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W11">
         <v>5</v>
@@ -1617,7 +1626,7 @@
         <v>5</v>
       </c>
       <c r="AC11">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1685,7 +1694,7 @@
         <v>7</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W12">
         <v>6</v>
@@ -1774,7 +1783,7 @@
         <v>7</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W13">
         <v>6</v>
@@ -1863,7 +1872,7 @@
         <v>6</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W14">
         <v>7</v>
@@ -1952,7 +1961,7 @@
         <v>6</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W15">
         <v>6</v>
@@ -2041,7 +2050,7 @@
         <v>6</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W16">
         <v>6</v>
@@ -2062,7 +2071,7 @@
         <v>5</v>
       </c>
       <c r="AC16">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -2130,7 +2139,7 @@
         <v>7</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W17">
         <v>8</v>
@@ -2219,7 +2228,7 @@
         <v>5</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W18">
         <v>6</v>
@@ -2308,7 +2317,7 @@
         <v>5</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W19">
         <v>6</v>
@@ -2397,7 +2406,7 @@
         <v>9</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W20">
         <v>10</v>
@@ -2486,7 +2495,7 @@
         <v>5</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W21">
         <v>6</v>
@@ -2507,7 +2516,7 @@
         <v>5</v>
       </c>
       <c r="AC21">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2575,7 +2584,7 @@
         <v>6</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W22">
         <v>6</v>
@@ -2664,7 +2673,7 @@
         <v>6</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W23">
         <v>6</v>
@@ -2753,7 +2762,7 @@
         <v>6</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W24">
         <v>7</v>
@@ -2842,7 +2851,7 @@
         <v>6</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W25">
         <v>6</v>
@@ -2863,7 +2872,7 @@
         <v>5</v>
       </c>
       <c r="AC25">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -2931,7 +2940,7 @@
         <v>8</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W26">
         <v>8</v>
@@ -3020,7 +3029,7 @@
         <v>9</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W27">
         <v>8</v>
@@ -3109,7 +3118,7 @@
         <v>8</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W28">
         <v>9</v>
@@ -3198,7 +3207,7 @@
         <v>6</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W29">
         <v>6</v>
@@ -3287,7 +3296,7 @@
         <v>6</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W30">
         <v>7</v>
@@ -3376,7 +3385,7 @@
         <v>8</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W31">
         <v>8</v>
@@ -3465,7 +3474,7 @@
         <v>6</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W32">
         <v>6</v>
@@ -5701,7 +5710,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>56</v>
@@ -5710,19 +5719,19 @@
         <v>29</v>
       </c>
       <c r="D4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2">
-        <v>93.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="G4" s="2">
-        <v>6.9</v>
+        <v>3.4</v>
       </c>
       <c r="H4">
-        <v>8.6</v>
+        <v>6.8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5733,7 +5742,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>57</v>
@@ -5742,19 +5751,19 @@
         <v>29</v>
       </c>
       <c r="D5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2">
-        <v>96.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="G5" s="2">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5765,7 +5774,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>58</v>
@@ -5786,7 +5795,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5797,7 +5806,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>59</v>
@@ -5818,7 +5827,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5829,7 +5838,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
         <v>60</v>
@@ -5850,7 +5859,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -5900,7 +5909,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5938,10 +5947,10 @@
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -5961,10 +5970,10 @@
         <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -5978,16 +5987,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920015</v>
+        <v>22330051920006</v>
       </c>
       <c r="B4" t="s">
         <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -6001,16 +6010,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920015</v>
+        <v>22330051920006</v>
       </c>
       <c r="B5" t="s">
         <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -6024,16 +6033,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920017</v>
+        <v>22330051920015</v>
       </c>
       <c r="B6" t="s">
         <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D6" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -6047,16 +6056,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920017</v>
+        <v>22330051920015</v>
       </c>
       <c r="B7" t="s">
         <v>67</v>
       </c>
       <c r="C7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D7" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -6070,22 +6079,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920382</v>
+        <v>22330051920017</v>
       </c>
       <c r="B8" t="s">
         <v>68</v>
       </c>
       <c r="C8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D8" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -6093,22 +6102,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920382</v>
+        <v>22330051920017</v>
       </c>
       <c r="B9" t="s">
         <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D9" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -6122,10 +6131,10 @@
         <v>69</v>
       </c>
       <c r="C10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D10" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
@@ -6145,10 +6154,10 @@
         <v>70</v>
       </c>
       <c r="C11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -6168,10 +6177,10 @@
         <v>71</v>
       </c>
       <c r="C12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D12" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
@@ -6191,10 +6200,10 @@
         <v>72</v>
       </c>
       <c r="C13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D13" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
@@ -6214,10 +6223,10 @@
         <v>73</v>
       </c>
       <c r="C14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D14" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
@@ -6234,13 +6243,13 @@
         <v>22330051920014</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D15" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
@@ -6260,10 +6269,10 @@
         <v>74</v>
       </c>
       <c r="C16" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D16" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
@@ -6283,10 +6292,10 @@
         <v>74</v>
       </c>
       <c r="C17" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D17" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
@@ -6306,10 +6315,10 @@
         <v>75</v>
       </c>
       <c r="C18" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D18" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E18" t="s">
         <v>10</v>
@@ -6329,10 +6338,10 @@
         <v>76</v>
       </c>
       <c r="C19" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D19" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
@@ -6349,13 +6358,13 @@
         <v>22330051920020</v>
       </c>
       <c r="B20" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="C20" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D20" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E20" t="s">
         <v>10</v>
@@ -6369,16 +6378,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>22330051920022</v>
+        <v>22330051920382</v>
       </c>
       <c r="B21" t="s">
         <v>77</v>
       </c>
       <c r="C21" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="D21" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E21" t="s">
         <v>10</v>
@@ -6392,16 +6401,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>22330051920322</v>
+        <v>22330051920022</v>
       </c>
       <c r="B22" t="s">
         <v>78</v>
       </c>
       <c r="C22" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="D22" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E22" t="s">
         <v>10</v>
@@ -6415,16 +6424,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>22330051920023</v>
+        <v>22330051920322</v>
       </c>
       <c r="B23" t="s">
         <v>79</v>
       </c>
       <c r="C23" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D23" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E23" t="s">
         <v>10</v>
@@ -6438,16 +6447,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>22330051920024</v>
+        <v>22330051920023</v>
       </c>
       <c r="B24" t="s">
         <v>80</v>
       </c>
       <c r="C24" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="D24" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E24" t="s">
         <v>10</v>
@@ -6461,16 +6470,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>22330051920025</v>
+        <v>22330051920024</v>
       </c>
       <c r="B25" t="s">
         <v>81</v>
       </c>
       <c r="C25" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="D25" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E25" t="s">
         <v>10</v>
@@ -6484,16 +6493,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>22330051920326</v>
+        <v>22330051920025</v>
       </c>
       <c r="B26" t="s">
         <v>82</v>
       </c>
       <c r="C26" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D26" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E26" t="s">
         <v>10</v>
@@ -6507,16 +6516,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>22330051920026</v>
+        <v>22330051920326</v>
       </c>
       <c r="B27" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D27" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E27" t="s">
         <v>10</v>
@@ -6530,16 +6539,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>22330051920173</v>
+        <v>22330051920026</v>
       </c>
       <c r="B28" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C28" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="D28" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E28" t="s">
         <v>10</v>
@@ -6553,16 +6562,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>22330051920330</v>
+        <v>22330051920173</v>
       </c>
       <c r="B29" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C29" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D29" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E29" t="s">
         <v>10</v>
@@ -6576,16 +6585,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>22330051920027</v>
+        <v>22330051920330</v>
       </c>
       <c r="B30" t="s">
         <v>83</v>
       </c>
       <c r="C30" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="D30" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E30" t="s">
         <v>10</v>
@@ -6599,16 +6608,16 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>22330051920332</v>
+        <v>22330051920027</v>
       </c>
       <c r="B31" t="s">
         <v>84</v>
       </c>
       <c r="C31" t="s">
-        <v>68</v>
+        <v>106</v>
       </c>
       <c r="D31" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E31" t="s">
         <v>10</v>
@@ -6617,6 +6626,29 @@
         <v>54</v>
       </c>
       <c r="G31">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32">
+        <v>22330051920332</v>
+      </c>
+      <c r="B32" t="s">
+        <v>85</v>
+      </c>
+      <c r="C32" t="s">
+        <v>77</v>
+      </c>
+      <c r="D32" t="s">
+        <v>132</v>
+      </c>
+      <c r="E32" t="s">
+        <v>10</v>
+      </c>
+      <c r="F32" t="s">
+        <v>54</v>
+      </c>
+      <c r="G32">
         <v>5</v>
       </c>
     </row>
